--- a/src/test/test-data/EmpID_Data.xlsx
+++ b/src/test/test-data/EmpID_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Playwright_ETR\src\test\test-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{41C39422-68F2-435D-B045-19FF26641914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F70403B6-E3B9-43BC-B2D4-190A28C026A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{909A3281-8CA7-4B20-967C-28D9B4ABE303}"/>
   </bookViews>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED0027B5-3DC5-4ADA-9929-7B93D8D4D95D}">
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -431,18 +431,10 @@
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>6666</v>
-      </c>
-      <c r="B2">
-        <v>6666</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
